--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J345"/>
+  <dimension ref="A1:J346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12860,6 +12860,42 @@
         <v>368.02</v>
       </c>
       <c r="J345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>358</v>
+      </c>
+      <c r="C346" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="D346" t="n">
+        <v>361.81</v>
+      </c>
+      <c r="E346" t="n">
+        <v>362.12</v>
+      </c>
+      <c r="F346" t="n">
+        <v>362.14</v>
+      </c>
+      <c r="G346" t="n">
+        <v>366.33</v>
+      </c>
+      <c r="H346" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="I346" t="n">
+        <v>369.19</v>
+      </c>
+      <c r="J346" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12876,7 +12912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16849,6 +16885,16 @@
       </c>
       <c r="B397" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -17017,28 +17063,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6267804339942634</v>
+        <v>0.6290130405113754</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1945645203428682</v>
+        <v>0.1964726306803415</v>
       </c>
       <c r="M2" t="n">
-        <v>6.948833832962499</v>
+        <v>6.940777276167761</v>
       </c>
       <c r="N2" t="n">
-        <v>75.79030683707974</v>
+        <v>75.61231489889168</v>
       </c>
       <c r="O2" t="n">
-        <v>8.705762852104332</v>
+        <v>8.69553419284242</v>
       </c>
       <c r="P2" t="n">
-        <v>337.7075139976029</v>
+        <v>337.6809226366328</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17095,28 +17141,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6539738207448008</v>
+        <v>0.6552477082753574</v>
       </c>
       <c r="J3" t="n">
+        <v>345</v>
+      </c>
+      <c r="K3" t="n">
         <v>344</v>
       </c>
-      <c r="K3" t="n">
-        <v>343</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2704139276026662</v>
+        <v>0.2722331401847932</v>
       </c>
       <c r="M3" t="n">
-        <v>5.705633759536006</v>
+        <v>5.695387138378597</v>
       </c>
       <c r="N3" t="n">
-        <v>53.87236481893953</v>
+        <v>53.72937647715307</v>
       </c>
       <c r="O3" t="n">
-        <v>7.339779616510262</v>
+        <v>7.33003250178013</v>
       </c>
       <c r="P3" t="n">
-        <v>338.9097600666636</v>
+        <v>338.8945912754696</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17173,28 +17219,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.668236042749179</v>
+        <v>0.6681813266486262</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2942547244430633</v>
+        <v>0.2953788410520577</v>
       </c>
       <c r="M4" t="n">
-        <v>5.538626188876137</v>
+        <v>5.522791877277788</v>
       </c>
       <c r="N4" t="n">
-        <v>49.91143118233064</v>
+        <v>49.76678540757604</v>
       </c>
       <c r="O4" t="n">
-        <v>7.064802274822037</v>
+        <v>7.054557775479342</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3289605176785</v>
+        <v>344.329612211369</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17251,28 +17297,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6292894601483402</v>
+        <v>0.6280407937737512</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2778230499586325</v>
+        <v>0.2780892254464962</v>
       </c>
       <c r="M5" t="n">
-        <v>5.279575172484033</v>
+        <v>5.269608313307282</v>
       </c>
       <c r="N5" t="n">
-        <v>47.97245662627566</v>
+        <v>47.84644674539012</v>
       </c>
       <c r="O5" t="n">
-        <v>6.926215173258456</v>
+        <v>6.917112601757334</v>
       </c>
       <c r="P5" t="n">
-        <v>347.6953615804737</v>
+        <v>347.7102337659857</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17329,28 +17375,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6301699034520856</v>
+        <v>0.629638829462186</v>
       </c>
       <c r="J6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2620790572851167</v>
+        <v>0.2628223053990945</v>
       </c>
       <c r="M6" t="n">
-        <v>5.524843319613455</v>
+        <v>5.511336234924968</v>
       </c>
       <c r="N6" t="n">
-        <v>52.10849482451938</v>
+        <v>51.95981465908017</v>
       </c>
       <c r="O6" t="n">
-        <v>7.218621393626306</v>
+        <v>7.208315660338424</v>
       </c>
       <c r="P6" t="n">
-        <v>346.4736147759351</v>
+        <v>346.4799401091539</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17407,28 +17453,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6197169176492883</v>
+        <v>0.6204088267837857</v>
       </c>
       <c r="J7" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K7" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2595098700605986</v>
+        <v>0.2609969801994797</v>
       </c>
       <c r="M7" t="n">
-        <v>5.387476815137832</v>
+        <v>5.375347408024531</v>
       </c>
       <c r="N7" t="n">
-        <v>51.07022757817068</v>
+        <v>50.92620205038897</v>
       </c>
       <c r="O7" t="n">
-        <v>7.146343650998787</v>
+        <v>7.136259668088667</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8467388606722</v>
+        <v>348.838497907592</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17485,28 +17531,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6703404494610848</v>
+        <v>0.670730338517553</v>
       </c>
       <c r="J8" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K8" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3028513215533937</v>
+        <v>0.3042694160651606</v>
       </c>
       <c r="M8" t="n">
-        <v>5.258199444111784</v>
+        <v>5.245075886690595</v>
       </c>
       <c r="N8" t="n">
-        <v>48.20615388283255</v>
+        <v>48.06769732560834</v>
       </c>
       <c r="O8" t="n">
-        <v>6.94306516481248</v>
+        <v>6.933087142507899</v>
       </c>
       <c r="P8" t="n">
-        <v>350.5580675086006</v>
+        <v>350.5534237522739</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17563,28 +17609,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5192027061034444</v>
+        <v>0.5176674404491473</v>
       </c>
       <c r="J9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1711628700397131</v>
+        <v>0.1710669389957639</v>
       </c>
       <c r="M9" t="n">
-        <v>5.728183384376372</v>
+        <v>5.719082263125023</v>
       </c>
       <c r="N9" t="n">
-        <v>60.83439983522612</v>
+        <v>60.67778228633259</v>
       </c>
       <c r="O9" t="n">
-        <v>7.799641006817309</v>
+        <v>7.789594487926351</v>
       </c>
       <c r="P9" t="n">
-        <v>358.1474947153732</v>
+        <v>358.1657804289037</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17622,7 +17668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J345"/>
+  <dimension ref="A1:J346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35561,6 +35607,58 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-45.80000231373682,170.7415101930047</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-45.80058595707029,170.74182499233476</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-45.80114586419045,170.74220324788897</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-45.801691952222406,170.7425840472962</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-45.802210832702556,170.74305609314837</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-45.80271906038718,170.7435800917012</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-45.803221169352454,170.74409290310456</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-45.80371371396602,170.74462864426016</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J346"/>
+  <dimension ref="A1:J347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12896,6 +12896,42 @@
         <v>369.19</v>
       </c>
       <c r="J346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>359.49</v>
+      </c>
+      <c r="C347" t="n">
+        <v>358.94</v>
+      </c>
+      <c r="D347" t="n">
+        <v>360.69</v>
+      </c>
+      <c r="E347" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="F347" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="G347" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="H347" t="n">
+        <v>368.22</v>
+      </c>
+      <c r="I347" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="J347" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12912,7 +12948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B398"/>
+  <dimension ref="A1:B399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16895,6 +16931,16 @@
       </c>
       <c r="B398" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -17063,28 +17109,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6290130405113754</v>
+        <v>0.6320675439839318</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1964726306803415</v>
+        <v>0.1987296689857239</v>
       </c>
       <c r="M2" t="n">
-        <v>6.940777276167761</v>
+        <v>6.937099877476289</v>
       </c>
       <c r="N2" t="n">
-        <v>75.61231489889168</v>
+        <v>75.47187765338553</v>
       </c>
       <c r="O2" t="n">
-        <v>8.69553419284242</v>
+        <v>8.687455188568487</v>
       </c>
       <c r="P2" t="n">
-        <v>337.6809226366328</v>
+        <v>337.6444421339282</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17141,28 +17187,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6552477082753574</v>
+        <v>0.6568693675393169</v>
       </c>
       <c r="J3" t="n">
+        <v>346</v>
+      </c>
+      <c r="K3" t="n">
         <v>345</v>
       </c>
-      <c r="K3" t="n">
-        <v>344</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2722331401847932</v>
+        <v>0.2742398073005753</v>
       </c>
       <c r="M3" t="n">
-        <v>5.695387138378597</v>
+        <v>5.686873055650172</v>
       </c>
       <c r="N3" t="n">
-        <v>53.72937647715307</v>
+        <v>53.59572302059129</v>
       </c>
       <c r="O3" t="n">
-        <v>7.33003250178013</v>
+        <v>7.32090998582767</v>
       </c>
       <c r="P3" t="n">
-        <v>338.8945912754696</v>
+        <v>338.875228088588</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17219,28 +17265,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6681813266486262</v>
+        <v>0.6674475249247281</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2953788410520577</v>
+        <v>0.2960647768487477</v>
       </c>
       <c r="M4" t="n">
-        <v>5.522791877277788</v>
+        <v>5.50974668251679</v>
       </c>
       <c r="N4" t="n">
-        <v>49.76678540757604</v>
+        <v>49.62745791730769</v>
       </c>
       <c r="O4" t="n">
-        <v>7.054557775479342</v>
+        <v>7.044675856085054</v>
       </c>
       <c r="P4" t="n">
-        <v>344.329612211369</v>
+        <v>344.3383761417472</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17297,28 +17343,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6280407937737512</v>
+        <v>0.6254257878747616</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2780892254464962</v>
+        <v>0.2772945307028832</v>
       </c>
       <c r="M5" t="n">
-        <v>5.269608313307282</v>
+        <v>5.265608077344487</v>
       </c>
       <c r="N5" t="n">
-        <v>47.84644674539012</v>
+        <v>47.76540093116832</v>
       </c>
       <c r="O5" t="n">
-        <v>6.917112601757334</v>
+        <v>6.911251762970895</v>
       </c>
       <c r="P5" t="n">
-        <v>347.7102337659857</v>
+        <v>347.741465267481</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17375,28 +17421,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.629638829462186</v>
+        <v>0.6277491363638708</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2628223053990945</v>
+        <v>0.262627381891947</v>
       </c>
       <c r="M6" t="n">
-        <v>5.511336234924968</v>
+        <v>5.504442924801467</v>
       </c>
       <c r="N6" t="n">
-        <v>51.95981465908017</v>
+        <v>51.83953186420186</v>
       </c>
       <c r="O6" t="n">
-        <v>7.208315660338424</v>
+        <v>7.19996749049618</v>
       </c>
       <c r="P6" t="n">
-        <v>346.4799401091539</v>
+        <v>346.5025090650589</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17453,28 +17499,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6204088267837857</v>
+        <v>0.6203977000946328</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2609969801994797</v>
+        <v>0.262068104584216</v>
       </c>
       <c r="M7" t="n">
-        <v>5.375347408024531</v>
+        <v>5.3598649254796</v>
       </c>
       <c r="N7" t="n">
-        <v>50.92620205038897</v>
+        <v>50.7790175316084</v>
       </c>
       <c r="O7" t="n">
-        <v>7.136259668088667</v>
+        <v>7.125939764803545</v>
       </c>
       <c r="P7" t="n">
-        <v>348.838497907592</v>
+        <v>348.8386307957087</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17531,28 +17577,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.670730338517553</v>
+        <v>0.6707189853738839</v>
       </c>
       <c r="J8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3042694160651606</v>
+        <v>0.3054451555066868</v>
       </c>
       <c r="M8" t="n">
-        <v>5.245075886690595</v>
+        <v>5.229966821553561</v>
       </c>
       <c r="N8" t="n">
-        <v>48.06769732560834</v>
+        <v>47.92877442378756</v>
       </c>
       <c r="O8" t="n">
-        <v>6.933087142507899</v>
+        <v>6.923061058793831</v>
       </c>
       <c r="P8" t="n">
-        <v>350.5534237522739</v>
+        <v>350.5535593449789</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17609,28 +17655,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5176674404491473</v>
+        <v>0.5162939009239836</v>
       </c>
       <c r="J9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1710669389957639</v>
+        <v>0.1710679682231816</v>
       </c>
       <c r="M9" t="n">
-        <v>5.719082263125023</v>
+        <v>5.709204676044123</v>
       </c>
       <c r="N9" t="n">
-        <v>60.67778228633259</v>
+        <v>60.51820459915545</v>
       </c>
       <c r="O9" t="n">
-        <v>7.789594487926351</v>
+        <v>7.779344740989144</v>
       </c>
       <c r="P9" t="n">
-        <v>358.1657804289037</v>
+        <v>358.1821848667487</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17668,7 +17714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J346"/>
+  <dimension ref="A1:J347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35659,6 +35705,58 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-45.799997899737484,170.7415282906751</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-45.800583940773876,170.74183284094215</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-45.801149764526244,170.74218996359795</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-45.80170168074615,170.74255764294992</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-45.802221480610115,170.74303087368253</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-45.80272448749875,170.74356749646222</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-45.80322438337912,170.7440860718952</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-45.80371224380586,170.74463156928218</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J347"/>
+  <dimension ref="A1:J348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12934,6 +12934,42 @@
       <c r="J347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>360.17</v>
+      </c>
+      <c r="C348" t="n">
+        <v>361.98</v>
+      </c>
+      <c r="D348" t="n">
+        <v>362</v>
+      </c>
+      <c r="E348" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="F348" t="n">
+        <v>362.06</v>
+      </c>
+      <c r="G348" t="n">
+        <v>364.29</v>
+      </c>
+      <c r="H348" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="I348" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B399"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16941,6 +16977,16 @@
       </c>
       <c r="B399" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -17109,28 +17155,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6320675439839318</v>
+        <v>0.6354648925685961</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1987296689857239</v>
+        <v>0.2011603099061438</v>
       </c>
       <c r="M2" t="n">
-        <v>6.937099877476289</v>
+        <v>6.934958379768338</v>
       </c>
       <c r="N2" t="n">
-        <v>75.47187765338553</v>
+        <v>75.34879612804488</v>
       </c>
       <c r="O2" t="n">
-        <v>8.687455188568487</v>
+        <v>8.680368432736302</v>
       </c>
       <c r="P2" t="n">
-        <v>337.6444421339282</v>
+        <v>337.6035579396821</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17187,28 +17233,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6568693675393169</v>
+        <v>0.6602205876223123</v>
       </c>
       <c r="J3" t="n">
+        <v>347</v>
+      </c>
+      <c r="K3" t="n">
         <v>346</v>
       </c>
-      <c r="K3" t="n">
-        <v>345</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2742398073005753</v>
+        <v>0.2770698597037049</v>
       </c>
       <c r="M3" t="n">
-        <v>5.686873055650172</v>
+        <v>5.686608899328789</v>
       </c>
       <c r="N3" t="n">
-        <v>53.59572302059129</v>
+        <v>53.5329861049774</v>
       </c>
       <c r="O3" t="n">
-        <v>7.32090998582767</v>
+        <v>7.316623955416691</v>
       </c>
       <c r="P3" t="n">
-        <v>338.875228088588</v>
+        <v>338.8349071695189</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17265,28 +17311,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6674475249247281</v>
+        <v>0.6674140911352661</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2960647768487477</v>
+        <v>0.2972388677337015</v>
       </c>
       <c r="M4" t="n">
-        <v>5.50974668251679</v>
+        <v>5.493998309050453</v>
       </c>
       <c r="N4" t="n">
-        <v>49.62745791730769</v>
+        <v>49.48444845066871</v>
       </c>
       <c r="O4" t="n">
-        <v>7.044675856085054</v>
+        <v>7.03451835242959</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3383761417472</v>
+        <v>344.3387784889036</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17343,28 +17389,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6254257878747616</v>
+        <v>0.6265462210036082</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2772945307028832</v>
+        <v>0.2791201959806823</v>
       </c>
       <c r="M5" t="n">
-        <v>5.265608077344487</v>
+        <v>5.256540248848589</v>
       </c>
       <c r="N5" t="n">
-        <v>47.76540093116832</v>
+        <v>47.63801776833456</v>
       </c>
       <c r="O5" t="n">
-        <v>6.911251762970895</v>
+        <v>6.902029974459293</v>
       </c>
       <c r="P5" t="n">
-        <v>347.741465267481</v>
+        <v>347.7279818098557</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17421,28 +17467,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6277491363638708</v>
+        <v>0.6270979450581402</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.262627381891947</v>
+        <v>0.2633221459547175</v>
       </c>
       <c r="M6" t="n">
-        <v>5.504442924801467</v>
+        <v>5.491647636650357</v>
       </c>
       <c r="N6" t="n">
-        <v>51.83953186420186</v>
+        <v>51.6936072520314</v>
       </c>
       <c r="O6" t="n">
-        <v>7.19996749049618</v>
+        <v>7.189826649650978</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5025090650589</v>
+        <v>346.5103455973344</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17499,28 +17545,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6203977000946328</v>
+        <v>0.6197961703104636</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L7" t="n">
-        <v>0.262068104584216</v>
+        <v>0.2627898701894225</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3598649254796</v>
+        <v>5.347235785239255</v>
       </c>
       <c r="N7" t="n">
-        <v>50.7790175316084</v>
+        <v>50.63564024443857</v>
       </c>
       <c r="O7" t="n">
-        <v>7.125939764803545</v>
+        <v>7.115872416256391</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8386307957087</v>
+        <v>348.8458696939047</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17577,28 +17623,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6707189853738839</v>
+        <v>0.6695466960128528</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3054451555066868</v>
+        <v>0.3058682565968189</v>
       </c>
       <c r="M8" t="n">
-        <v>5.229966821553561</v>
+        <v>5.219953747328786</v>
       </c>
       <c r="N8" t="n">
-        <v>47.92877442378756</v>
+        <v>47.80189301417559</v>
       </c>
       <c r="O8" t="n">
-        <v>6.923061058793831</v>
+        <v>6.913891307662826</v>
       </c>
       <c r="P8" t="n">
-        <v>350.5535593449789</v>
+        <v>350.5676668481552</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17655,28 +17701,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5162939009239836</v>
+        <v>0.51375244805327</v>
       </c>
       <c r="J9" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K9" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1710679682231816</v>
+        <v>0.1703577085853654</v>
       </c>
       <c r="M9" t="n">
-        <v>5.709204676044123</v>
+        <v>5.704812978432441</v>
       </c>
       <c r="N9" t="n">
-        <v>60.51820459915545</v>
+        <v>60.39663687980636</v>
       </c>
       <c r="O9" t="n">
-        <v>7.779344740989144</v>
+        <v>7.771527319633275</v>
       </c>
       <c r="P9" t="n">
-        <v>358.1821848667487</v>
+        <v>358.2127690856607</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17714,7 +17760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J347"/>
+  <dimension ref="A1:J348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35757,6 +35803,58 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-45.799995885293875,170.74153655001368</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-45.800574510703356,170.74186954826783</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-45.80114520252618,170.7422055014739</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-45.801674675690606,170.74263093775096</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-45.80221120468196,170.74305521211915</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-45.8027286876102,170.74355774884083</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-45.80323362370343,170.74406643216403</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-45.80372211487969,170.74461192984595</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J348"/>
+  <dimension ref="A1:J349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12970,6 +12970,42 @@
       <c r="J348" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="C349" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="D349" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="E349" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="F349" t="n">
+        <v>360.62</v>
+      </c>
+      <c r="G349" t="n">
+        <v>362.61</v>
+      </c>
+      <c r="H349" t="n">
+        <v>363.78</v>
+      </c>
+      <c r="I349" t="n">
+        <v>366.62</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12984,7 +13020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B400"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16987,6 +17023,16 @@
       </c>
       <c r="B400" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -17155,28 +17201,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6354648925685961</v>
+        <v>0.639524975349004</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2011603099061438</v>
+        <v>0.2038434880804305</v>
       </c>
       <c r="M2" t="n">
-        <v>6.934958379768338</v>
+        <v>6.936255090747872</v>
       </c>
       <c r="N2" t="n">
-        <v>75.34879612804488</v>
+        <v>75.2684452629891</v>
       </c>
       <c r="O2" t="n">
-        <v>8.680368432736302</v>
+        <v>8.675738888589784</v>
       </c>
       <c r="P2" t="n">
-        <v>337.6035579396821</v>
+        <v>337.5546534036761</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17233,28 +17279,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6602205876223123</v>
+        <v>0.6646634583835157</v>
       </c>
       <c r="J3" t="n">
+        <v>348</v>
+      </c>
+      <c r="K3" t="n">
         <v>347</v>
       </c>
-      <c r="K3" t="n">
-        <v>346</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2770698597037049</v>
+        <v>0.2802928876127578</v>
       </c>
       <c r="M3" t="n">
-        <v>5.686608899328789</v>
+        <v>5.691550682094379</v>
       </c>
       <c r="N3" t="n">
-        <v>53.5329861049774</v>
+        <v>53.54228690823262</v>
       </c>
       <c r="O3" t="n">
-        <v>7.316623955416691</v>
+        <v>7.317259521722092</v>
       </c>
       <c r="P3" t="n">
-        <v>338.8349071695189</v>
+        <v>338.7814024756029</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17311,28 +17357,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6674140911352661</v>
+        <v>0.668802011418543</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2972388677337015</v>
+        <v>0.2992313655971779</v>
       </c>
       <c r="M4" t="n">
-        <v>5.493998309050453</v>
+        <v>5.486315304014103</v>
       </c>
       <c r="N4" t="n">
-        <v>49.48444845066871</v>
+        <v>49.35816418747955</v>
       </c>
       <c r="O4" t="n">
-        <v>7.03451835242959</v>
+        <v>7.02553657648151</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3387784889036</v>
+        <v>344.3220607023121</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17389,28 +17435,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6265462210036082</v>
+        <v>0.6274658300089907</v>
       </c>
       <c r="J5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2791201959806823</v>
+        <v>0.2808284943029339</v>
       </c>
       <c r="M5" t="n">
-        <v>5.256540248848589</v>
+        <v>5.246440656168912</v>
       </c>
       <c r="N5" t="n">
-        <v>47.63801776833456</v>
+        <v>47.50811267540717</v>
       </c>
       <c r="O5" t="n">
-        <v>6.902029974459293</v>
+        <v>6.892612906250225</v>
       </c>
       <c r="P5" t="n">
-        <v>347.7279818098557</v>
+        <v>347.7169049293714</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17467,28 +17513,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6270979450581402</v>
+        <v>0.625596764776419</v>
       </c>
       <c r="J6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2633221459547175</v>
+        <v>0.2634256274249792</v>
       </c>
       <c r="M6" t="n">
-        <v>5.491647636650357</v>
+        <v>5.482902227329311</v>
       </c>
       <c r="N6" t="n">
-        <v>51.6936072520314</v>
+        <v>51.56367783488105</v>
       </c>
       <c r="O6" t="n">
-        <v>7.189826649650978</v>
+        <v>7.180785321598261</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5103455973344</v>
+        <v>346.5284276240096</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17545,28 +17591,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6197961703104636</v>
+        <v>0.6182059993157409</v>
       </c>
       <c r="J7" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K7" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2627898701894225</v>
+        <v>0.2628163027207852</v>
       </c>
       <c r="M7" t="n">
-        <v>5.347235785239255</v>
+        <v>5.33956038920754</v>
       </c>
       <c r="N7" t="n">
-        <v>50.63564024443857</v>
+        <v>50.51102344432475</v>
       </c>
       <c r="O7" t="n">
-        <v>7.115872416256391</v>
+        <v>7.10711076629067</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8458696939047</v>
+        <v>348.8650236321058</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17623,28 +17669,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6695466960128528</v>
+        <v>0.6668606132027683</v>
       </c>
       <c r="J8" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K8" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3058682565968189</v>
+        <v>0.3051041613618205</v>
       </c>
       <c r="M8" t="n">
-        <v>5.219953747328786</v>
+        <v>5.216781511128993</v>
       </c>
       <c r="N8" t="n">
-        <v>47.80189301417559</v>
+        <v>47.72413124373287</v>
       </c>
       <c r="O8" t="n">
-        <v>6.913891307662826</v>
+        <v>6.908265429449918</v>
       </c>
       <c r="P8" t="n">
-        <v>350.5676668481552</v>
+        <v>350.6000212706154</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17701,28 +17747,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.51375244805327</v>
+        <v>0.510672331655981</v>
       </c>
       <c r="J9" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K9" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1703577085853654</v>
+        <v>0.1692807191053224</v>
       </c>
       <c r="M9" t="n">
-        <v>5.704812978432441</v>
+        <v>5.7029646572298</v>
       </c>
       <c r="N9" t="n">
-        <v>60.39663687980636</v>
+        <v>60.30145184774254</v>
       </c>
       <c r="O9" t="n">
-        <v>7.771527319633275</v>
+        <v>7.765400945717004</v>
       </c>
       <c r="P9" t="n">
-        <v>358.2127690856607</v>
+        <v>358.249869724096</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17760,7 +17806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J348"/>
+  <dimension ref="A1:J349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35855,6 +35901,58 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-45.79999224151929,170.7415514896982</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-45.80056843078308,170.74189321482672</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-45.801136740184454,170.74223432363416</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-45.80167593369116,170.74262752339843</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-45.80221790030996,170.74303935359129</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-45.80273661590812,170.7435393488324</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-45.80324668067741,170.744038680359</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-45.80372720793234,170.7446017967299</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J349"/>
+  <dimension ref="A1:J354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13006,6 +13006,186 @@
       <c r="J349" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="C350" t="n">
+        <v>361.02</v>
+      </c>
+      <c r="D350" t="n">
+        <v>362.51</v>
+      </c>
+      <c r="E350" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="F350" t="n">
+        <v>359.16</v>
+      </c>
+      <c r="G350" t="n">
+        <v>361.69</v>
+      </c>
+      <c r="H350" t="n">
+        <v>362.65</v>
+      </c>
+      <c r="I350" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>358.45</v>
+      </c>
+      <c r="C351" t="n">
+        <v>360.47</v>
+      </c>
+      <c r="D351" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="E351" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="F351" t="n">
+        <v>358.81</v>
+      </c>
+      <c r="G351" t="n">
+        <v>361.31</v>
+      </c>
+      <c r="H351" t="n">
+        <v>362.05</v>
+      </c>
+      <c r="I351" t="n">
+        <v>366.67</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="C352" t="n">
+        <v>358.51</v>
+      </c>
+      <c r="D352" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="E352" t="n">
+        <v>360</v>
+      </c>
+      <c r="F352" t="n">
+        <v>357.05</v>
+      </c>
+      <c r="G352" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="H352" t="n">
+        <v>359.37</v>
+      </c>
+      <c r="I352" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="C353" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="D353" t="n">
+        <v>362.87</v>
+      </c>
+      <c r="E353" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="F353" t="n">
+        <v>359.06</v>
+      </c>
+      <c r="G353" t="n">
+        <v>361.71</v>
+      </c>
+      <c r="H353" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="I353" t="n">
+        <v>367.21</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>358.47</v>
+      </c>
+      <c r="C354" t="n">
+        <v>360.2</v>
+      </c>
+      <c r="D354" t="n">
+        <v>363.86</v>
+      </c>
+      <c r="E354" t="n">
+        <v>363.22</v>
+      </c>
+      <c r="F354" t="n">
+        <v>360.03</v>
+      </c>
+      <c r="G354" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="H354" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="I354" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13020,7 +13200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17033,6 +17213,56 @@
       </c>
       <c r="B401" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -17201,28 +17431,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.639524975349004</v>
+        <v>0.6482416625341535</v>
       </c>
       <c r="J2" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2038434880804305</v>
+        <v>0.2126540299165789</v>
       </c>
       <c r="M2" t="n">
-        <v>6.936255090747872</v>
+        <v>6.883073595607013</v>
       </c>
       <c r="N2" t="n">
-        <v>75.2684452629891</v>
+        <v>74.33942955391505</v>
       </c>
       <c r="O2" t="n">
-        <v>8.675738888589784</v>
+        <v>8.622031637260156</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5546534036761</v>
+        <v>337.4491097290272</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17279,28 +17509,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6646634583835157</v>
+        <v>0.6744749313313562</v>
       </c>
       <c r="J3" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2802928876127578</v>
+        <v>0.2913612675111612</v>
       </c>
       <c r="M3" t="n">
-        <v>5.691550682094379</v>
+        <v>5.6568060498611</v>
       </c>
       <c r="N3" t="n">
-        <v>53.54228690823262</v>
+        <v>52.95366945507795</v>
       </c>
       <c r="O3" t="n">
-        <v>7.317259521722092</v>
+        <v>7.276927198693</v>
       </c>
       <c r="P3" t="n">
-        <v>338.7814024756029</v>
+        <v>338.6626373398738</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17357,28 +17587,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.668802011418543</v>
+        <v>0.6705061372931281</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2992313655971779</v>
+        <v>0.3061952186143208</v>
       </c>
       <c r="M4" t="n">
-        <v>5.486315304014103</v>
+        <v>5.423261401537638</v>
       </c>
       <c r="N4" t="n">
-        <v>49.35816418747955</v>
+        <v>48.6740800062587</v>
       </c>
       <c r="O4" t="n">
-        <v>7.02553657648151</v>
+        <v>6.976681159853781</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3220607023121</v>
+        <v>344.3014190990465</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17435,28 +17665,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6274658300089907</v>
+        <v>0.6220867014212217</v>
       </c>
       <c r="J5" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2808284943029339</v>
+        <v>0.2827175037461023</v>
       </c>
       <c r="M5" t="n">
-        <v>5.246440656168912</v>
+        <v>5.194907275086851</v>
       </c>
       <c r="N5" t="n">
-        <v>47.50811267540717</v>
+        <v>46.91294782280595</v>
       </c>
       <c r="O5" t="n">
-        <v>6.892612906250225</v>
+        <v>6.849302725300287</v>
       </c>
       <c r="P5" t="n">
-        <v>347.7169049293714</v>
+        <v>347.7820628800321</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17513,28 +17743,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.625596764776419</v>
+        <v>0.6130331658910679</v>
       </c>
       <c r="J6" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2634256274249792</v>
+        <v>0.2599870108490833</v>
       </c>
       <c r="M6" t="n">
-        <v>5.482902227329311</v>
+        <v>5.463238699004552</v>
       </c>
       <c r="N6" t="n">
-        <v>51.56367783488105</v>
+        <v>51.11036555001861</v>
       </c>
       <c r="O6" t="n">
-        <v>7.180785321598261</v>
+        <v>7.149151386704482</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5284276240096</v>
+        <v>346.6805515582636</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17591,28 +17821,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6182059993157409</v>
+        <v>0.6072961728374782</v>
       </c>
       <c r="J7" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K7" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2628163027207852</v>
+        <v>0.2605480475865137</v>
       </c>
       <c r="M7" t="n">
-        <v>5.33956038920754</v>
+        <v>5.315816686895442</v>
       </c>
       <c r="N7" t="n">
-        <v>50.51102344432475</v>
+        <v>50.01227128913858</v>
       </c>
       <c r="O7" t="n">
-        <v>7.10711076629067</v>
+        <v>7.071935469808713</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8650236321058</v>
+        <v>348.997115660052</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17669,28 +17899,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6668606132027683</v>
+        <v>0.6500581913846306</v>
       </c>
       <c r="J8" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3051041613618205</v>
+        <v>0.2979655409952202</v>
       </c>
       <c r="M8" t="n">
-        <v>5.216781511128993</v>
+        <v>5.217800525314219</v>
       </c>
       <c r="N8" t="n">
-        <v>47.72413124373287</v>
+        <v>47.57186868159917</v>
       </c>
       <c r="O8" t="n">
-        <v>6.908265429449918</v>
+        <v>6.897236307507463</v>
       </c>
       <c r="P8" t="n">
-        <v>350.6000212706154</v>
+        <v>350.8034535274458</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17747,28 +17977,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.510672331655981</v>
+        <v>0.496712230692626</v>
       </c>
       <c r="J9" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K9" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1692807191053224</v>
+        <v>0.164538315014097</v>
       </c>
       <c r="M9" t="n">
-        <v>5.7029646572298</v>
+        <v>5.686923467029123</v>
       </c>
       <c r="N9" t="n">
-        <v>60.30145184774254</v>
+        <v>59.8580483694972</v>
       </c>
       <c r="O9" t="n">
-        <v>7.765400945717004</v>
+        <v>7.736798328087478</v>
       </c>
       <c r="P9" t="n">
-        <v>358.249869724096</v>
+        <v>358.4188634262306</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -17806,7 +18036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J349"/>
+  <dimension ref="A1:J354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35953,6 +36183,266 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-45.80000278772315,170.74150824963053</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-45.800577488621656,170.74185795648208</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-45.801143426479776,170.74221155056995</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-45.801683439758975,170.7426071510918</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-45.80222468893048,170.7430232748023</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-45.802740957593755,170.74352927263516</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-45.80325235543701,170.74402661899362</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-45.80373077831922,170.74459469310108</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-45.800000980650076,170.74151565874436</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-45.80057919472015,170.74185131535427</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-45.80114067534841,170.74222092073765</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-45.80168671055829,170.74259827377213</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-45.802226316339166,170.74301942029751</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-45.80274275089844,170.74352511072715</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-45.80325536858316,170.74402021472778</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-45.80372694540388,170.74460231905553</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-45.8000077645776,170.74148784419984</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-45.80058527463156,170.74182764878654</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-45.80114753576312,170.7421975546216</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-45.80170084208056,170.74255991918702</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-45.8022344998779,170.74300003764156</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-45.80275020726881,170.7435078059489</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-45.80326882729804,170.74399160899884</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-45.80374206703941,170.7445722330922</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-45.80000382456813,170.7415039984994</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-45.80058173835716,170.74184141403575</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-45.80114217279975,170.7422158205199</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-45.80169170062258,170.74258473016712</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-45.8022251539044,170.74302217351524</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-45.8027408632093,170.74352949168295</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-45.80324994491983,170.74403174240572</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-45.8037241100963,170.74460796017183</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-45.80000092140177,170.7415159016661</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-45.80058003225926,170.74184805516413</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-45.80113872517886,170.74222756288128</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-45.80168733955809,170.74259656659515</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-45.802220643656895,170.74303285599896</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-45.80273350122001,170.74354657740776</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-45.803238846493855,170.74405533144355</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-45.803702635257224,170.74465068638634</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0504/nzd0504.xlsx
+++ b/data/nzd0504/nzd0504.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:J356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13184,6 +13184,78 @@
         <v>371.3</v>
       </c>
       <c r="J354" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="C355" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D355" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="E355" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="F355" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="G355" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="H355" t="n">
+        <v>365.58</v>
+      </c>
+      <c r="I355" t="n">
+        <v>370.71</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="C356" t="n">
+        <v>359.21</v>
+      </c>
+      <c r="D356" t="n">
+        <v>364.19</v>
+      </c>
+      <c r="E356" t="n">
+        <v>364.63</v>
+      </c>
+      <c r="F356" t="n">
+        <v>362.62</v>
+      </c>
+      <c r="G356" t="n">
+        <v>365.66</v>
+      </c>
+      <c r="H356" t="n">
+        <v>367.05</v>
+      </c>
+      <c r="I356" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="J356" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13200,7 +13272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B406"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17263,6 +17335,26 @@
       </c>
       <c r="B406" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -17431,28 +17523,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6482416625341535</v>
+        <v>0.651719467436276</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2126540299165789</v>
+        <v>0.2162025117850204</v>
       </c>
       <c r="M2" t="n">
-        <v>6.883073595607013</v>
+        <v>6.862370317947766</v>
       </c>
       <c r="N2" t="n">
-        <v>74.33942955391505</v>
+        <v>73.97366658104477</v>
       </c>
       <c r="O2" t="n">
-        <v>8.622031637260156</v>
+        <v>8.600794531963007</v>
       </c>
       <c r="P2" t="n">
-        <v>337.4491097290272</v>
+        <v>337.4068168584765</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17509,28 +17601,28 @@
         <v>0.1167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6744749313313562</v>
+        <v>0.677920319605587</v>
       </c>
       <c r="J3" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2913612675111612</v>
+        <v>0.2955592078700208</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6568060498611</v>
+        <v>5.640804428485561</v>
       </c>
       <c r="N3" t="n">
-        <v>52.95366945507795</v>
+        <v>52.70770440783566</v>
       </c>
       <c r="O3" t="n">
-        <v>7.276927198693</v>
+        <v>7.26000719061873</v>
       </c>
       <c r="P3" t="n">
-        <v>338.6626373398738</v>
+        <v>338.6207463337677</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17587,28 +17679,28 @@
         <v>0.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6705061372931281</v>
+        <v>0.6727096752472556</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3061952186143208</v>
+        <v>0.3098637892276638</v>
       </c>
       <c r="M4" t="n">
-        <v>5.423261401537638</v>
+        <v>5.405218704688711</v>
       </c>
       <c r="N4" t="n">
-        <v>48.6740800062587</v>
+        <v>48.42080004339201</v>
       </c>
       <c r="O4" t="n">
-        <v>6.976681159853781</v>
+        <v>6.958505589808204</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3014190990465</v>
+        <v>344.2746209394405</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17665,28 +17757,28 @@
         <v>0.0728</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6220867014212217</v>
+        <v>0.6221724592435361</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2827175037461023</v>
+        <v>0.2850260513301546</v>
       </c>
       <c r="M5" t="n">
-        <v>5.194907275086851</v>
+        <v>5.166242345568622</v>
       </c>
       <c r="N5" t="n">
-        <v>46.91294782280595</v>
+        <v>46.64873302146206</v>
       </c>
       <c r="O5" t="n">
-        <v>6.849302725300287</v>
+        <v>6.82998777608438</v>
       </c>
       <c r="P5" t="n">
-        <v>347.7820628800321</v>
+        <v>347.7810193216434</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17743,28 +17835,28 @@
         <v>0.0824</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6130331658910679</v>
+        <v>0.6118450595708655</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2599870108490833</v>
+        <v>0.2613454041346093</v>
       </c>
       <c r="M6" t="n">
-        <v>5.463238699004552</v>
+        <v>5.437914500367121</v>
       </c>
       <c r="N6" t="n">
-        <v>51.11036555001861</v>
+        <v>50.83023033220705</v>
       </c>
       <c r="O6" t="n">
-        <v>7.149151386704482</v>
+        <v>7.129532266019073</v>
       </c>
       <c r="P6" t="n">
-        <v>346.6805515582636</v>
+        <v>346.6949972188219</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17821,28 +17913,28 @@
         <v>0.094</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6072961728374782</v>
+        <v>0.6069848342084057</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K7" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2605480475865137</v>
+        <v>0.2624791577375072</v>
       </c>
       <c r="M7" t="n">
-        <v>5.315816686895442</v>
+        <v>5.28951887766345</v>
       </c>
       <c r="N7" t="n">
-        <v>50.01227128913858</v>
+        <v>49.73335754659372</v>
       </c>
       <c r="O7" t="n">
-        <v>7.071935469808713</v>
+        <v>7.052188138910768</v>
       </c>
       <c r="P7" t="n">
-        <v>348.997115660052</v>
+        <v>349.0008978249277</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17899,28 +17991,28 @@
         <v>0.0582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6500581913846306</v>
+        <v>0.6478921087298271</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K8" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2979655409952202</v>
+        <v>0.298785366095064</v>
       </c>
       <c r="M8" t="n">
-        <v>5.217800525314219</v>
+        <v>5.198034196477219</v>
       </c>
       <c r="N8" t="n">
-        <v>47.57186868159917</v>
+        <v>47.32707390721863</v>
       </c>
       <c r="O8" t="n">
-        <v>6.897236307507463</v>
+        <v>6.879467559863818</v>
       </c>
       <c r="P8" t="n">
-        <v>350.8034535274458</v>
+        <v>350.829791760894</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -17977,28 +18069,28 @@
         <v>0.0586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.496712230692626</v>
+        <v>0.4961683699003329</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.164538315014097</v>
+        <v>0.1657574197069828</v>
       </c>
       <c r="M9" t="n">
-        <v>5.686923467029123</v>
+        <v>5.657790417169229</v>
       </c>
       <c r="N9" t="n">
-        <v>59.8580483694972</v>
+        <v>59.52373173696976</v>
       </c>
       <c r="O9" t="n">
-        <v>7.736798328087478</v>
+        <v>7.715162456939566</v>
       </c>
       <c r="P9" t="n">
-        <v>358.4188634262306</v>
+        <v>358.42547416628</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18036,7 +18128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:J356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36443,6 +36535,110 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-45.80000148426065,170.7415135939094</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-45.800579597979734,170.74184974563312</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-45.801137401849296,170.7422320700499</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-45.8016822656257,170.74261033782167</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-45.802213808537566,170.7430490449143</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-45.80272849884116,170.74355818693618</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-45.80323764123464,170.74405789314847</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-45.80370573309569,170.74464452294907</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-45.800003794944,170.7415041199603</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-45.8005831032352,170.74183610113275</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-45.80113757597162,170.74223147700144</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-45.80168142695903,170.74261261405724</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-45.802208600826006,170.7430613793234</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-45.80272222226974,170.74357275360572</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-45.80323025902051,170.74407358358863</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-45.80370006247587,170.74465580517267</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
